--- a/ReinsurancePortfolio/TestPlans/SupportingData/Template/BuySell 01 BuySellPricing_TestCases.xlsx
+++ b/ReinsurancePortfolio/TestPlans/SupportingData/Template/BuySell 01 BuySellPricing_TestCases.xlsx
@@ -5,33 +5,35 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARAPL_USER\Desktop\Tests\ReinsurancePortfolio\TestPlans\SupportingData\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARAPL_USER\Desktop\UI Testing\Pricing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871D0B56-E98C-4BA1-BA90-217E1E53E12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FC6562-FF9B-45E6-8DDE-B663CDD6B8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="9" r:id="rId1"/>
-    <sheet name="Buy" sheetId="6" r:id="rId2"/>
-    <sheet name="Sell" sheetId="7" r:id="rId3"/>
-    <sheet name="Pricing" sheetId="8" r:id="rId4"/>
-    <sheet name="BuySell_Pricing" sheetId="1" r:id="rId5"/>
-    <sheet name="Summary_Pricing" sheetId="2" r:id="rId6"/>
-    <sheet name="PortfolioPricingParameters" sheetId="10" r:id="rId7"/>
-    <sheet name="Instructions" sheetId="3" r:id="rId8"/>
-    <sheet name="BuySellResults" sheetId="4" r:id="rId9"/>
-    <sheet name="SummaryPricingResults" sheetId="5" r:id="rId10"/>
+    <sheet name="Buy" sheetId="6" state="hidden" r:id="rId2"/>
+    <sheet name="Sell" sheetId="7" state="hidden" r:id="rId3"/>
+    <sheet name="Pricing" sheetId="8" state="hidden" r:id="rId4"/>
+    <sheet name="Prereq" sheetId="12" r:id="rId5"/>
+    <sheet name="Prereq_result" sheetId="11" r:id="rId6"/>
+    <sheet name="BuySell_Pricing" sheetId="1" r:id="rId7"/>
+    <sheet name="Summary_Pricing" sheetId="2" r:id="rId8"/>
+    <sheet name="PortfolioPricingParameters" sheetId="10" r:id="rId9"/>
+    <sheet name="Instructions" sheetId="3" r:id="rId10"/>
+    <sheet name="BuySellResults" sheetId="4" r:id="rId11"/>
+    <sheet name="SummaryPricingResults" sheetId="5" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Buy!$A$56:$Y$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">BuySell_Pricing!$A$5:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">PortfolioPricingParameters!$A$1:$O$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BuySell_Pricing!$A$5:$X$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">PortfolioPricingParameters!$A$1:$O$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sell!$A$1:$P$148</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Summary_Pricing!$A$7:$Z$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Summary_Pricing!$A$7:$Z$144</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -49,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7188" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7249" uniqueCount="817">
   <si>
     <t>Pricing Results</t>
   </si>
@@ -2340,14 +2342,190 @@
   <si>
     <t>CB-Fish Pond Re Ltd. Series 2024-1 Class A Reset 2025</t>
   </si>
+  <si>
+    <t>ReportID</t>
+  </si>
+  <si>
+    <t>InvestedAUM</t>
+  </si>
+  <si>
+    <t>PortfolioId</t>
+  </si>
+  <si>
+    <t>TotalPremium</t>
+  </si>
+  <si>
+    <t>FederalExciseTax</t>
+  </si>
+  <si>
+    <t>AcqExpenses</t>
+  </si>
+  <si>
+    <t>FrontingFee</t>
+  </si>
+  <si>
+    <t>PortNonModeledAAL</t>
+  </si>
+  <si>
+    <t>PortfolioAAL</t>
+  </si>
+  <si>
+    <t>NotionalShortAggLimit</t>
+  </si>
+  <si>
+    <t>NotionalShortOccLimit</t>
+  </si>
+  <si>
+    <t>LeverageExpense</t>
+  </si>
+  <si>
+    <t>InvestmentIncome</t>
+  </si>
+  <si>
+    <t>PnLInvestmentIncome</t>
+  </si>
+  <si>
+    <t>OpOrgExpenses</t>
+  </si>
+  <si>
+    <t>ManagementFee</t>
+  </si>
+  <si>
+    <t>Carry</t>
+  </si>
+  <si>
+    <t>Leverage</t>
+  </si>
+  <si>
+    <t>TotalAUM</t>
+  </si>
+  <si>
+    <t>StandardDeviation</t>
+  </si>
+  <si>
+    <t>TVAR50</t>
+  </si>
+  <si>
+    <t>AEP500</t>
+  </si>
+  <si>
+    <t>TC_PF_001</t>
+  </si>
+  <si>
+    <t>TC_PF_002</t>
+  </si>
+  <si>
+    <t>TC_PF_003</t>
+  </si>
+  <si>
+    <t>TC_PF_004</t>
+  </si>
+  <si>
+    <t>TC_PF_005</t>
+  </si>
+  <si>
+    <t>TC_PF_006</t>
+  </si>
+  <si>
+    <t>TC_PF_007</t>
+  </si>
+  <si>
+    <t>TC_PF_008</t>
+  </si>
+  <si>
+    <t>TC_PF_009</t>
+  </si>
+  <si>
+    <t>TC_PF_010</t>
+  </si>
+  <si>
+    <t>TC_PF_011</t>
+  </si>
+  <si>
+    <t>TC_PF_012</t>
+  </si>
+  <si>
+    <t>TC_PF_013</t>
+  </si>
+  <si>
+    <t>TC_PF_014</t>
+  </si>
+  <si>
+    <t>TC_PF_015</t>
+  </si>
+  <si>
+    <t>TC_PF_016</t>
+  </si>
+  <si>
+    <t>TC_PF_017</t>
+  </si>
+  <si>
+    <t>TC_PF_018</t>
+  </si>
+  <si>
+    <t>TC_PF_019</t>
+  </si>
+  <si>
+    <t>TC_PF_020</t>
+  </si>
+  <si>
+    <t>TC_PF_021</t>
+  </si>
+  <si>
+    <t>TC_PF_022</t>
+  </si>
+  <si>
+    <t>TC_PF_023</t>
+  </si>
+  <si>
+    <t>TC_PF_024</t>
+  </si>
+  <si>
+    <t>TC_PF_025</t>
+  </si>
+  <si>
+    <t>TC_PF_026</t>
+  </si>
+  <si>
+    <t>TC_PF_027</t>
+  </si>
+  <si>
+    <t>TC_PF_028</t>
+  </si>
+  <si>
+    <t>TC_PF_029</t>
+  </si>
+  <si>
+    <t>TC_PF_030</t>
+  </si>
+  <si>
+    <t>TC_PF_031</t>
+  </si>
+  <si>
+    <t>TC_PF_032</t>
+  </si>
+  <si>
+    <t>TC_PF_033</t>
+  </si>
+  <si>
+    <t>TC_PF_034</t>
+  </si>
+  <si>
+    <t>TC_PF_035</t>
+  </si>
+  <si>
+    <t>TestCaseID</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.############################"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -2573,7 +2751,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2752,6 +2930,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3125,11 +3309,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3359,67 +3544,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3463,6 +3597,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3481,8 +3668,11 @@
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="23" fillId="35" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -3798,206 +3988,215 @@
       <c r="A2" s="44" t="s">
         <v>722</v>
       </c>
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="97" t="s">
         <v>736</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="116"/>
-    </row>
-    <row r="3" spans="1:10" s="109" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="98"/>
+    </row>
+    <row r="3" spans="1:10" s="99" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="45" t="s">
         <v>723</v>
       </c>
-      <c r="B4" s="117" t="s">
+      <c r="B4" s="100" t="s">
         <v>737</v>
       </c>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-    </row>
-    <row r="5" spans="1:10" s="109" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="101"/>
+    </row>
+    <row r="5" spans="1:10" s="99" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:10" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="102" t="s">
         <v>724</v>
       </c>
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="105" t="s">
         <v>725</v>
       </c>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="123"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="106"/>
     </row>
     <row r="7" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="120"/>
+      <c r="A7" s="103"/>
       <c r="B7" s="46" t="s">
         <v>738</v>
       </c>
-      <c r="C7" s="124" t="s">
+      <c r="C7" s="107" t="s">
         <v>739</v>
       </c>
-      <c r="D7" s="124"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="125"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="108"/>
     </row>
     <row r="8" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="120"/>
+      <c r="A8" s="103"/>
       <c r="B8" s="46" t="s">
         <v>726</v>
       </c>
-      <c r="C8" s="124" t="s">
+      <c r="C8" s="107" t="s">
         <v>740</v>
       </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="125"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="108"/>
     </row>
     <row r="9" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="120"/>
+      <c r="A9" s="103"/>
       <c r="B9" s="46" t="s">
         <v>727</v>
       </c>
-      <c r="C9" s="126" t="s">
+      <c r="C9" s="109" t="s">
         <v>741</v>
       </c>
-      <c r="D9" s="127"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="127"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="128"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="111"/>
     </row>
     <row r="10" spans="1:10" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="121"/>
+      <c r="A10" s="104"/>
       <c r="B10" s="47" t="s">
         <v>728</v>
       </c>
-      <c r="C10" s="129" t="s">
+      <c r="C10" s="112" t="s">
         <v>742</v>
       </c>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
-      <c r="I10" s="129"/>
-      <c r="J10" s="130"/>
-    </row>
-    <row r="11" spans="1:10" s="109" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" s="109" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="113"/>
+    </row>
+    <row r="11" spans="1:10" s="99" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" s="99" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="110" t="s">
+      <c r="A13" s="118" t="s">
         <v>729</v>
       </c>
       <c r="B13" s="48" t="s">
         <v>730</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="114"/>
+      <c r="C13" s="121"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="121"/>
+      <c r="H13" s="121"/>
+      <c r="I13" s="121"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="111"/>
+      <c r="A14" s="119"/>
       <c r="B14" s="49" t="s">
         <v>731</v>
       </c>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="106"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="115"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="111"/>
+      <c r="A15" s="119"/>
       <c r="B15" s="49" t="s">
         <v>732</v>
       </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="106"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="115"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="111"/>
+      <c r="A16" s="119"/>
       <c r="B16" s="49" t="s">
         <v>733</v>
       </c>
-      <c r="C16" s="105"/>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="106"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="115"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="111"/>
+      <c r="A17" s="119"/>
       <c r="B17" s="49" t="s">
         <v>734</v>
       </c>
-      <c r="C17" s="105"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="106"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="115"/>
     </row>
     <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="112"/>
+      <c r="A18" s="120"/>
       <c r="B18" s="50" t="s">
         <v>735</v>
       </c>
-      <c r="C18" s="107"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="108"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A11:XFD11"/>
+    <mergeCell ref="A12:XFD12"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="C16:J16"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="A3:XFD3"/>
     <mergeCell ref="B4:J4"/>
@@ -4008,21 +4207,1415 @@
     <mergeCell ref="C8:J8"/>
     <mergeCell ref="C9:J9"/>
     <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="A11:XFD11"/>
-    <mergeCell ref="A12:XFD12"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C16:J16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="20"/>
+    </row>
+    <row r="3" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="20" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="20" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="20" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="20" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="20" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="20"/>
+    </row>
+    <row r="10" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="20" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="20"/>
+    </row>
+    <row r="13" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="20" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="20"/>
+    </row>
+    <row r="16" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="20" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="20" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="20" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="20" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="20"/>
+    </row>
+    <row r="22" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="20" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="20"/>
+    </row>
+    <row r="25" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="20"/>
+    </row>
+    <row r="28" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Sheet8"/>
+  <dimension ref="A1:BF40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="9" width="19" customWidth="1"/>
+    <col min="10" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="17" width="15" customWidth="1"/>
+    <col min="18" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="20" customWidth="1"/>
+    <col min="23" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="15" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="19" customWidth="1"/>
+    <col min="28" max="28" width="21" customWidth="1"/>
+    <col min="29" max="29" width="16" customWidth="1"/>
+    <col min="30" max="30" width="25" customWidth="1"/>
+    <col min="31" max="32" width="18" customWidth="1"/>
+    <col min="33" max="52" width="15" customWidth="1"/>
+    <col min="53" max="53" width="18" customWidth="1"/>
+    <col min="54" max="54" width="21" customWidth="1"/>
+    <col min="55" max="55" width="15" customWidth="1"/>
+    <col min="56" max="56" width="18" customWidth="1"/>
+    <col min="57" max="58" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:58" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="125"/>
+      <c r="P1" s="125"/>
+      <c r="Q1" s="125"/>
+      <c r="R1" s="125"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
+      <c r="U1" s="125"/>
+      <c r="V1" s="125"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
+      <c r="Y1" s="125"/>
+      <c r="Z1" s="125"/>
+      <c r="AA1" s="125"/>
+      <c r="AB1" s="125"/>
+      <c r="AC1" s="125"/>
+      <c r="AD1" s="125"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="125"/>
+      <c r="AG1" s="125"/>
+      <c r="AH1" s="125"/>
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="125"/>
+      <c r="AK1" s="125"/>
+      <c r="AL1" s="125"/>
+      <c r="AM1" s="125"/>
+      <c r="AN1" s="125"/>
+      <c r="AO1" s="125"/>
+      <c r="AP1" s="125"/>
+      <c r="AQ1" s="125"/>
+      <c r="AR1" s="125"/>
+      <c r="AS1" s="125"/>
+      <c r="AT1" s="125"/>
+      <c r="AU1" s="125"/>
+      <c r="AV1" s="125"/>
+      <c r="AW1" s="125"/>
+      <c r="AX1" s="125"/>
+      <c r="AY1" s="125"/>
+      <c r="AZ1" s="125"/>
+    </row>
+    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="W2" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="X2" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y2" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z2" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB2" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC2" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD2" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE2" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA2" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="BB2" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="BC2" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="BD2" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="BE2" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="BF2" s="27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
+      <c r="AA3" s="26"/>
+      <c r="AB3" s="26"/>
+      <c r="AC3" s="26"/>
+      <c r="AD3" s="26"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="26"/>
+    </row>
+    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="BA4" s="29"/>
+      <c r="BB4" s="29"/>
+    </row>
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+    </row>
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+    </row>
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+    </row>
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29"/>
+      <c r="AC8" s="29"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="29"/>
+    </row>
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="29"/>
+    </row>
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="Q10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="AC10" s="29"/>
+      <c r="BC10" s="29"/>
+      <c r="BD10" s="29"/>
+      <c r="BE10" s="29"/>
+      <c r="BF10" s="29"/>
+    </row>
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="29"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="29"/>
+      <c r="BA11" s="29"/>
+      <c r="BB11" s="29"/>
+    </row>
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="29"/>
+      <c r="N12" s="28"/>
+      <c r="Q12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
+      <c r="Z12" s="29"/>
+      <c r="AC12" s="29"/>
+    </row>
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
+      <c r="BA13" s="29"/>
+      <c r="BB13" s="29"/>
+    </row>
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="29"/>
+    </row>
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="29"/>
+      <c r="BA15" s="29"/>
+      <c r="BB15" s="29"/>
+    </row>
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="29"/>
+      <c r="N16" s="28"/>
+      <c r="Q16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="Z16" s="29"/>
+      <c r="AC16" s="29"/>
+    </row>
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="29"/>
+      <c r="AC17" s="29"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="29"/>
+      <c r="BA17" s="29"/>
+      <c r="BB17" s="29"/>
+    </row>
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="29"/>
+      <c r="N18" s="28"/>
+      <c r="Q18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="Z18" s="29"/>
+      <c r="AC18" s="29"/>
+    </row>
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="29"/>
+      <c r="AC19" s="29"/>
+      <c r="AD19" s="29"/>
+      <c r="AE19" s="29"/>
+      <c r="AF19" s="29"/>
+      <c r="BA19" s="29"/>
+      <c r="BB19" s="29"/>
+    </row>
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="29"/>
+      <c r="N20" s="28"/>
+      <c r="Q20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="Z20" s="29"/>
+      <c r="AC20" s="29"/>
+    </row>
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="29"/>
+      <c r="X21" s="29"/>
+      <c r="Y21" s="29"/>
+      <c r="Z21" s="29"/>
+      <c r="AA21" s="29"/>
+      <c r="AC21" s="29"/>
+      <c r="AD21" s="29"/>
+      <c r="AE21" s="29"/>
+      <c r="AF21" s="29"/>
+      <c r="BA21" s="29"/>
+      <c r="BB21" s="29"/>
+    </row>
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="29"/>
+      <c r="N22" s="28"/>
+      <c r="Q22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="Z22" s="29"/>
+      <c r="AC22" s="29"/>
+    </row>
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
+      <c r="AA23" s="29"/>
+      <c r="AC23" s="29"/>
+      <c r="AD23" s="29"/>
+      <c r="AE23" s="29"/>
+      <c r="AF23" s="29"/>
+      <c r="BA23" s="29"/>
+      <c r="BB23" s="29"/>
+    </row>
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="29"/>
+      <c r="N24" s="28"/>
+      <c r="Q24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="Z24" s="29"/>
+      <c r="AC24" s="29"/>
+    </row>
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="29"/>
+      <c r="AA25" s="29"/>
+      <c r="AC25" s="29"/>
+      <c r="AD25" s="29"/>
+      <c r="AE25" s="29"/>
+      <c r="AF25" s="29"/>
+      <c r="BA25" s="29"/>
+      <c r="BB25" s="29"/>
+    </row>
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A26" s="28"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="29"/>
+      <c r="N26" s="28"/>
+      <c r="Q26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="Z26" s="29"/>
+      <c r="AC26" s="29"/>
+    </row>
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="29"/>
+      <c r="AA27" s="29"/>
+      <c r="AC27" s="29"/>
+      <c r="AD27" s="29"/>
+      <c r="AE27" s="29"/>
+      <c r="AF27" s="29"/>
+      <c r="BA27" s="29"/>
+      <c r="BB27" s="29"/>
+    </row>
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A28" s="28"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="29"/>
+      <c r="AC28" s="29"/>
+      <c r="AD28" s="29"/>
+      <c r="AE28" s="29"/>
+      <c r="AF28" s="29"/>
+    </row>
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
+      <c r="AC29" s="29"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="29"/>
+      <c r="AF29" s="29"/>
+      <c r="BA29" s="29"/>
+      <c r="BB29" s="29"/>
+    </row>
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A30" s="28"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="29"/>
+      <c r="AA30" s="29"/>
+      <c r="AB30" s="29"/>
+      <c r="AC30" s="29"/>
+      <c r="AD30" s="29"/>
+      <c r="AE30" s="29"/>
+      <c r="AF30" s="29"/>
+    </row>
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="Q31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="AC31" s="29"/>
+      <c r="BC31" s="29"/>
+      <c r="BE31" s="29"/>
+    </row>
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="Q32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="AC32" s="29"/>
+      <c r="BC32" s="29"/>
+      <c r="BD32" s="29"/>
+      <c r="BE32" s="29"/>
+      <c r="BF32" s="29"/>
+    </row>
+    <row r="33" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A33" s="28"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="Q33" s="29"/>
+      <c r="T33" s="29"/>
+      <c r="AC33" s="29"/>
+      <c r="BC33" s="29"/>
+      <c r="BE33" s="29"/>
+    </row>
+    <row r="34" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A34" s="28"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="Q34" s="29"/>
+      <c r="T34" s="29"/>
+      <c r="AC34" s="29"/>
+      <c r="BC34" s="29"/>
+      <c r="BE34" s="29"/>
+    </row>
+    <row r="35" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A35" s="28"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="Q35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="AC35" s="29"/>
+      <c r="BC35" s="29"/>
+      <c r="BE35" s="29"/>
+    </row>
+    <row r="36" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A36" s="28"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="Q36" s="29"/>
+      <c r="T36" s="29"/>
+      <c r="AC36" s="29"/>
+      <c r="BC36" s="29"/>
+      <c r="BE36" s="29"/>
+    </row>
+    <row r="37" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="Q37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="AC37" s="29"/>
+      <c r="BC37" s="29"/>
+      <c r="BE37" s="29"/>
+    </row>
+    <row r="38" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="Q38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="AC38" s="29"/>
+      <c r="BC38" s="29"/>
+      <c r="BE38" s="29"/>
+    </row>
+    <row r="39" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A39" s="28"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="Q39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="AC39" s="29"/>
+      <c r="BC39" s="29"/>
+      <c r="BE39" s="29"/>
+    </row>
+    <row r="40" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A40" s="28"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="Q40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="AC40" s="29"/>
+      <c r="BC40" s="29"/>
+      <c r="BE40" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AZ1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:BQ33"/>
@@ -4093,60 +5686,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:69" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
-      <c r="AD1" s="97"/>
-      <c r="AE1" s="97"/>
-      <c r="AF1" s="97"/>
-      <c r="AG1" s="97"/>
-      <c r="AH1" s="97"/>
-      <c r="AI1" s="97"/>
-      <c r="AJ1" s="97"/>
-      <c r="AK1" s="97"/>
-      <c r="AL1" s="97"/>
-      <c r="AM1" s="97"/>
-      <c r="AN1" s="97"/>
-      <c r="AO1" s="97"/>
-      <c r="AP1" s="97"/>
-      <c r="AQ1" s="97"/>
-      <c r="AR1" s="97"/>
-      <c r="AS1" s="97"/>
-      <c r="AT1" s="97"/>
-      <c r="AU1" s="97"/>
-      <c r="AV1" s="97"/>
-      <c r="AW1" s="97"/>
-      <c r="AX1" s="97"/>
-      <c r="AY1" s="97"/>
-      <c r="AZ1" s="97"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="125"/>
+      <c r="P1" s="125"/>
+      <c r="Q1" s="125"/>
+      <c r="R1" s="125"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
+      <c r="U1" s="125"/>
+      <c r="V1" s="125"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
+      <c r="Y1" s="125"/>
+      <c r="Z1" s="125"/>
+      <c r="AA1" s="125"/>
+      <c r="AB1" s="125"/>
+      <c r="AC1" s="125"/>
+      <c r="AD1" s="125"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="125"/>
+      <c r="AG1" s="125"/>
+      <c r="AH1" s="125"/>
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="125"/>
+      <c r="AK1" s="125"/>
+      <c r="AL1" s="125"/>
+      <c r="AM1" s="125"/>
+      <c r="AN1" s="125"/>
+      <c r="AO1" s="125"/>
+      <c r="AP1" s="125"/>
+      <c r="AQ1" s="125"/>
+      <c r="AR1" s="125"/>
+      <c r="AS1" s="125"/>
+      <c r="AT1" s="125"/>
+      <c r="AU1" s="125"/>
+      <c r="AV1" s="125"/>
+      <c r="AW1" s="125"/>
+      <c r="AX1" s="125"/>
+      <c r="AY1" s="125"/>
+      <c r="AZ1" s="125"/>
     </row>
     <row r="2" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
@@ -30472,6 +32065,2932 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA61F6C-6B30-4D80-B51B-736DE325C790}">
+  <sheetPr codeName="Sheet10"/>
+  <dimension ref="A1:Z36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" style="140" customWidth="1"/>
+    <col min="3" max="4" width="12.109375" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" s="95" t="s">
+        <v>759</v>
+      </c>
+      <c r="B1" s="139" t="s">
+        <v>760</v>
+      </c>
+      <c r="C1" s="95" t="s">
+        <v>761</v>
+      </c>
+      <c r="D1" s="95" t="s">
+        <v>816</v>
+      </c>
+      <c r="E1" s="95" t="s">
+        <v>762</v>
+      </c>
+      <c r="F1" s="95" t="s">
+        <v>763</v>
+      </c>
+      <c r="G1" s="95" t="s">
+        <v>764</v>
+      </c>
+      <c r="H1" s="95" t="s">
+        <v>765</v>
+      </c>
+      <c r="I1" s="95" t="s">
+        <v>766</v>
+      </c>
+      <c r="J1" s="95" t="s">
+        <v>767</v>
+      </c>
+      <c r="K1" s="95" t="s">
+        <v>768</v>
+      </c>
+      <c r="L1" s="95" t="s">
+        <v>769</v>
+      </c>
+      <c r="M1" s="95" t="s">
+        <v>770</v>
+      </c>
+      <c r="N1" s="95" t="s">
+        <v>771</v>
+      </c>
+      <c r="O1" s="95" t="s">
+        <v>772</v>
+      </c>
+      <c r="P1" s="95" t="s">
+        <v>773</v>
+      </c>
+      <c r="Q1" s="95" t="s">
+        <v>774</v>
+      </c>
+      <c r="R1" s="95" t="s">
+        <v>775</v>
+      </c>
+      <c r="S1" s="95" t="s">
+        <v>776</v>
+      </c>
+      <c r="T1" s="95" t="s">
+        <v>160</v>
+      </c>
+      <c r="U1" s="95" t="s">
+        <v>777</v>
+      </c>
+      <c r="V1" s="95" t="s">
+        <v>778</v>
+      </c>
+      <c r="W1" s="95" t="s">
+        <v>779</v>
+      </c>
+      <c r="X1" s="95" t="s">
+        <v>780</v>
+      </c>
+      <c r="Y1" s="95" t="s">
+        <v>590</v>
+      </c>
+      <c r="Z1" s="95" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>103</v>
+      </c>
+      <c r="B2" s="140">
+        <v>2500000</v>
+      </c>
+      <c r="C2">
+        <v>900000001</v>
+      </c>
+      <c r="D2" t="s">
+        <v>781</v>
+      </c>
+      <c r="E2">
+        <v>210525</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>32915.4</v>
+      </c>
+      <c r="K2" s="96">
+        <v>2500000</v>
+      </c>
+      <c r="L2" s="96">
+        <v>2500000</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>19350</v>
+      </c>
+      <c r="O2">
+        <v>19350</v>
+      </c>
+      <c r="P2">
+        <v>11400</v>
+      </c>
+      <c r="Q2">
+        <v>36000</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.83333199999999996</v>
+      </c>
+      <c r="T2">
+        <v>8.4209900000000004E-2</v>
+      </c>
+      <c r="U2" s="96">
+        <v>3000000</v>
+      </c>
+      <c r="V2">
+        <v>104158</v>
+      </c>
+      <c r="W2">
+        <v>559522</v>
+      </c>
+      <c r="X2">
+        <v>750000</v>
+      </c>
+      <c r="Y2">
+        <v>6.8845700000000001</v>
+      </c>
+      <c r="Z2">
+        <v>1.1187400000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>283</v>
+      </c>
+      <c r="B3" s="140">
+        <v>2500000</v>
+      </c>
+      <c r="C3">
+        <v>900000002</v>
+      </c>
+      <c r="D3" t="s">
+        <v>782</v>
+      </c>
+      <c r="E3">
+        <v>210525</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>32915.4</v>
+      </c>
+      <c r="K3" s="96">
+        <v>2500000</v>
+      </c>
+      <c r="L3" s="96">
+        <v>2500000</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>19350</v>
+      </c>
+      <c r="O3">
+        <v>19350</v>
+      </c>
+      <c r="P3">
+        <v>11400</v>
+      </c>
+      <c r="Q3">
+        <v>36000</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0.83333199999999996</v>
+      </c>
+      <c r="T3">
+        <v>8.4209900000000004E-2</v>
+      </c>
+      <c r="U3" s="96">
+        <v>3000000</v>
+      </c>
+      <c r="V3">
+        <v>104158</v>
+      </c>
+      <c r="W3">
+        <v>559522</v>
+      </c>
+      <c r="X3">
+        <v>750000</v>
+      </c>
+      <c r="Y3">
+        <v>6.8845700000000001</v>
+      </c>
+      <c r="Z3">
+        <v>1.1187400000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>284</v>
+      </c>
+      <c r="B4" s="140">
+        <v>2500000</v>
+      </c>
+      <c r="C4">
+        <v>900000003</v>
+      </c>
+      <c r="D4" t="s">
+        <v>783</v>
+      </c>
+      <c r="E4">
+        <v>210525</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>32915.4</v>
+      </c>
+      <c r="K4" s="96">
+        <v>2500000</v>
+      </c>
+      <c r="L4" s="96">
+        <v>2500000</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>19350</v>
+      </c>
+      <c r="O4">
+        <v>19350</v>
+      </c>
+      <c r="P4">
+        <v>11400</v>
+      </c>
+      <c r="Q4">
+        <v>36000</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0.83333199999999996</v>
+      </c>
+      <c r="T4">
+        <v>8.4209900000000004E-2</v>
+      </c>
+      <c r="U4" s="96">
+        <v>3000000</v>
+      </c>
+      <c r="V4">
+        <v>104158</v>
+      </c>
+      <c r="W4">
+        <v>559522</v>
+      </c>
+      <c r="X4">
+        <v>750000</v>
+      </c>
+      <c r="Y4">
+        <v>6.8845700000000001</v>
+      </c>
+      <c r="Z4">
+        <v>1.1187400000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>285</v>
+      </c>
+      <c r="B5" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C5">
+        <v>900000004</v>
+      </c>
+      <c r="D5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E5">
+        <v>386821</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>59981.7</v>
+      </c>
+      <c r="K5" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L5" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>9675</v>
+      </c>
+      <c r="O5">
+        <v>9675</v>
+      </c>
+      <c r="P5">
+        <v>7600</v>
+      </c>
+      <c r="Q5">
+        <v>24000</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>1.38018</v>
+      </c>
+      <c r="T5">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U5" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V5">
+        <v>305947</v>
+      </c>
+      <c r="W5" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X5" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y5">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z5">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>286</v>
+      </c>
+      <c r="B6" s="140">
+        <v>2500000</v>
+      </c>
+      <c r="C6">
+        <v>900000005</v>
+      </c>
+      <c r="D6" t="s">
+        <v>785</v>
+      </c>
+      <c r="E6">
+        <v>720085</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>64342.5</v>
+      </c>
+      <c r="K6" s="96">
+        <v>5142220</v>
+      </c>
+      <c r="L6" s="96">
+        <v>5142220</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>19350</v>
+      </c>
+      <c r="O6">
+        <v>19350</v>
+      </c>
+      <c r="P6">
+        <v>11400</v>
+      </c>
+      <c r="Q6">
+        <v>36000</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>1.71407</v>
+      </c>
+      <c r="T6">
+        <v>0.14003399999999999</v>
+      </c>
+      <c r="U6" s="96">
+        <v>3000000</v>
+      </c>
+      <c r="V6">
+        <v>235305</v>
+      </c>
+      <c r="W6" s="96">
+        <v>1346030</v>
+      </c>
+      <c r="X6" s="96">
+        <v>1659780</v>
+      </c>
+      <c r="Y6">
+        <v>6.7803000000000004</v>
+      </c>
+      <c r="Z6">
+        <v>1.1017999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>287</v>
+      </c>
+      <c r="B7" s="140">
+        <v>2500000</v>
+      </c>
+      <c r="C7">
+        <v>900000006</v>
+      </c>
+      <c r="D7" t="s">
+        <v>786</v>
+      </c>
+      <c r="E7">
+        <v>505575</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>44479</v>
+      </c>
+      <c r="K7" s="96">
+        <v>4267990</v>
+      </c>
+      <c r="L7" s="96">
+        <v>4267990</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>19350</v>
+      </c>
+      <c r="O7">
+        <v>19350</v>
+      </c>
+      <c r="P7">
+        <v>11400</v>
+      </c>
+      <c r="Q7">
+        <v>36000</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>1.42266</v>
+      </c>
+      <c r="T7">
+        <v>0.11845700000000001</v>
+      </c>
+      <c r="U7" s="96">
+        <v>3000000</v>
+      </c>
+      <c r="V7">
+        <v>174274</v>
+      </c>
+      <c r="W7" s="96">
+        <v>1065120</v>
+      </c>
+      <c r="X7" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="Y7">
+        <v>6.9173799999999996</v>
+      </c>
+      <c r="Z7">
+        <v>1.1240699999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>288</v>
+      </c>
+      <c r="B8" s="140">
+        <v>2500000</v>
+      </c>
+      <c r="C8">
+        <v>900000007</v>
+      </c>
+      <c r="D8" t="s">
+        <v>787</v>
+      </c>
+      <c r="E8">
+        <v>210525</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>32915.4</v>
+      </c>
+      <c r="K8" s="96">
+        <v>2500000</v>
+      </c>
+      <c r="L8" s="96">
+        <v>2500000</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>19350</v>
+      </c>
+      <c r="O8">
+        <v>19350</v>
+      </c>
+      <c r="P8">
+        <v>11400</v>
+      </c>
+      <c r="Q8">
+        <v>36000</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0.83333199999999996</v>
+      </c>
+      <c r="T8">
+        <v>8.4209900000000004E-2</v>
+      </c>
+      <c r="U8" s="96">
+        <v>3000000</v>
+      </c>
+      <c r="V8">
+        <v>104158</v>
+      </c>
+      <c r="W8">
+        <v>559522</v>
+      </c>
+      <c r="X8">
+        <v>750000</v>
+      </c>
+      <c r="Y8">
+        <v>6.8845700000000001</v>
+      </c>
+      <c r="Z8">
+        <v>1.1187400000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>289</v>
+      </c>
+      <c r="B9" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C9">
+        <v>900000008</v>
+      </c>
+      <c r="D9" t="s">
+        <v>788</v>
+      </c>
+      <c r="E9">
+        <v>386821</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>59981.7</v>
+      </c>
+      <c r="K9" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L9" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>9675</v>
+      </c>
+      <c r="O9">
+        <v>9675</v>
+      </c>
+      <c r="P9">
+        <v>7600</v>
+      </c>
+      <c r="Q9">
+        <v>24000</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>1.38018</v>
+      </c>
+      <c r="T9">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U9" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V9">
+        <v>305947</v>
+      </c>
+      <c r="W9" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X9" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y9">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z9">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>290</v>
+      </c>
+      <c r="B10" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C10">
+        <v>900000009</v>
+      </c>
+      <c r="D10" t="s">
+        <v>789</v>
+      </c>
+      <c r="E10">
+        <v>386821</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>59981.7</v>
+      </c>
+      <c r="K10" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L10" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>9675</v>
+      </c>
+      <c r="O10">
+        <v>9675</v>
+      </c>
+      <c r="P10">
+        <v>100000</v>
+      </c>
+      <c r="Q10">
+        <v>240000</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>1.38018</v>
+      </c>
+      <c r="T10">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U10" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V10">
+        <v>305947</v>
+      </c>
+      <c r="W10" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X10" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y10">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z10">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>291</v>
+      </c>
+      <c r="B11" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C11">
+        <v>900000010</v>
+      </c>
+      <c r="D11" t="s">
+        <v>790</v>
+      </c>
+      <c r="E11">
+        <v>386821</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>59981.7</v>
+      </c>
+      <c r="K11" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L11" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>12500</v>
+      </c>
+      <c r="O11">
+        <v>12500</v>
+      </c>
+      <c r="P11">
+        <v>7600</v>
+      </c>
+      <c r="Q11">
+        <v>24000</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>1.38018</v>
+      </c>
+      <c r="T11">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U11" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V11">
+        <v>305947</v>
+      </c>
+      <c r="W11" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X11" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y11">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z11">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>292</v>
+      </c>
+      <c r="B12" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C12">
+        <v>900000011</v>
+      </c>
+      <c r="D12" t="s">
+        <v>791</v>
+      </c>
+      <c r="E12">
+        <v>386821</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>59981.7</v>
+      </c>
+      <c r="K12" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L12" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>12500</v>
+      </c>
+      <c r="O12">
+        <v>12500</v>
+      </c>
+      <c r="P12">
+        <v>7600</v>
+      </c>
+      <c r="Q12">
+        <v>24000</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>1.38018</v>
+      </c>
+      <c r="T12">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U12" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V12">
+        <v>305947</v>
+      </c>
+      <c r="W12" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X12" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y12">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z12">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>293</v>
+      </c>
+      <c r="B13" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C13">
+        <v>900000012</v>
+      </c>
+      <c r="D13" t="s">
+        <v>792</v>
+      </c>
+      <c r="E13">
+        <v>386821</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>59981.7</v>
+      </c>
+      <c r="K13" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L13" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>12500</v>
+      </c>
+      <c r="O13">
+        <v>12500</v>
+      </c>
+      <c r="P13">
+        <v>7600</v>
+      </c>
+      <c r="Q13">
+        <v>24000</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>1.38018</v>
+      </c>
+      <c r="T13">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U13" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V13">
+        <v>305947</v>
+      </c>
+      <c r="W13" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X13" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y13">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z13">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>294</v>
+      </c>
+      <c r="B14" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C14">
+        <v>900000013</v>
+      </c>
+      <c r="D14" t="s">
+        <v>793</v>
+      </c>
+      <c r="E14">
+        <v>386821</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>59981.7</v>
+      </c>
+      <c r="K14" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L14" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>12500</v>
+      </c>
+      <c r="O14">
+        <v>12500</v>
+      </c>
+      <c r="P14">
+        <v>7600</v>
+      </c>
+      <c r="Q14">
+        <v>24000</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>1.38018</v>
+      </c>
+      <c r="T14">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U14" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V14">
+        <v>305947</v>
+      </c>
+      <c r="W14" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X14" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y14">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z14">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>295</v>
+      </c>
+      <c r="B15" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C15">
+        <v>900000014</v>
+      </c>
+      <c r="D15" t="s">
+        <v>794</v>
+      </c>
+      <c r="E15">
+        <v>386821</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>59981.7</v>
+      </c>
+      <c r="K15" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L15" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>12500</v>
+      </c>
+      <c r="O15">
+        <v>12500</v>
+      </c>
+      <c r="P15">
+        <v>7600</v>
+      </c>
+      <c r="Q15">
+        <v>24000</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>1.38018</v>
+      </c>
+      <c r="T15">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U15" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V15">
+        <v>305947</v>
+      </c>
+      <c r="W15" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X15" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y15">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z15">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>296</v>
+      </c>
+      <c r="B16" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C16">
+        <v>900000015</v>
+      </c>
+      <c r="D16" t="s">
+        <v>795</v>
+      </c>
+      <c r="E16">
+        <v>386821</v>
+      </c>
+      <c r="F16">
+        <v>58023.1</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>59981.7</v>
+      </c>
+      <c r="K16" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L16" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>12500</v>
+      </c>
+      <c r="O16">
+        <v>12500</v>
+      </c>
+      <c r="P16">
+        <v>7600</v>
+      </c>
+      <c r="Q16">
+        <v>24000</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>1.38018</v>
+      </c>
+      <c r="T16">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U16" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V16">
+        <v>305947</v>
+      </c>
+      <c r="W16" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X16" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y16">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z16">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>297</v>
+      </c>
+      <c r="B17" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C17">
+        <v>900000016</v>
+      </c>
+      <c r="D17" t="s">
+        <v>796</v>
+      </c>
+      <c r="E17">
+        <v>386821</v>
+      </c>
+      <c r="F17">
+        <v>58023.1</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>59981.7</v>
+      </c>
+      <c r="K17" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="L17" s="96">
+        <v>2760360</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>12500</v>
+      </c>
+      <c r="O17">
+        <v>12500</v>
+      </c>
+      <c r="P17">
+        <v>7600</v>
+      </c>
+      <c r="Q17">
+        <v>24000</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>1.38018</v>
+      </c>
+      <c r="T17">
+        <v>0.14013400000000001</v>
+      </c>
+      <c r="U17" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V17">
+        <v>305947</v>
+      </c>
+      <c r="W17" s="96">
+        <v>1964350</v>
+      </c>
+      <c r="X17" s="96">
+        <v>2158680</v>
+      </c>
+      <c r="Y17">
+        <v>6.8597000000000001</v>
+      </c>
+      <c r="Z17">
+        <v>1.1147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>298</v>
+      </c>
+      <c r="B18" s="140">
+        <v>1450000</v>
+      </c>
+      <c r="C18">
+        <v>900000017</v>
+      </c>
+      <c r="D18" t="s">
+        <v>797</v>
+      </c>
+      <c r="E18">
+        <v>145707</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>29455.5</v>
+      </c>
+      <c r="K18" s="96">
+        <v>1750000</v>
+      </c>
+      <c r="L18" s="96">
+        <v>1750000</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>21285</v>
+      </c>
+      <c r="O18">
+        <v>21285</v>
+      </c>
+      <c r="P18">
+        <v>7600</v>
+      </c>
+      <c r="Q18">
+        <v>24000</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0.875</v>
+      </c>
+      <c r="T18">
+        <v>8.3261199999999994E-2</v>
+      </c>
+      <c r="U18" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V18">
+        <v>110272</v>
+      </c>
+      <c r="W18">
+        <v>549335</v>
+      </c>
+      <c r="X18">
+        <v>750000</v>
+      </c>
+      <c r="Y18">
+        <v>6.53423</v>
+      </c>
+      <c r="Z18">
+        <v>1.0618099999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>299</v>
+      </c>
+      <c r="B19" s="140">
+        <v>1700000</v>
+      </c>
+      <c r="C19">
+        <v>900000018</v>
+      </c>
+      <c r="D19" t="s">
+        <v>798</v>
+      </c>
+      <c r="E19">
+        <v>171734</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>36679.699999999997</v>
+      </c>
+      <c r="K19" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="L19" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>11610</v>
+      </c>
+      <c r="O19">
+        <v>11610</v>
+      </c>
+      <c r="P19">
+        <v>7600</v>
+      </c>
+      <c r="Q19">
+        <v>24000</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>8.5866999999999999E-2</v>
+      </c>
+      <c r="U19" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V19">
+        <v>145020</v>
+      </c>
+      <c r="W19">
+        <v>813837</v>
+      </c>
+      <c r="X19" s="96">
+        <v>1000000</v>
+      </c>
+      <c r="Y19">
+        <v>6.6426499999999997</v>
+      </c>
+      <c r="Z19">
+        <v>1.0794299999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>300</v>
+      </c>
+      <c r="B20" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C20">
+        <v>900000019</v>
+      </c>
+      <c r="D20" t="s">
+        <v>799</v>
+      </c>
+      <c r="E20">
+        <v>122756</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>23676.2</v>
+      </c>
+      <c r="K20" s="96">
+        <v>1550000</v>
+      </c>
+      <c r="L20" s="96">
+        <v>1550000</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>9675</v>
+      </c>
+      <c r="O20">
+        <v>9675</v>
+      </c>
+      <c r="P20">
+        <v>7600</v>
+      </c>
+      <c r="Q20">
+        <v>24000</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="T20">
+        <v>7.9197199999999995E-2</v>
+      </c>
+      <c r="U20" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V20">
+        <v>86448.3</v>
+      </c>
+      <c r="W20">
+        <v>401459</v>
+      </c>
+      <c r="X20">
+        <v>550000</v>
+      </c>
+      <c r="Y20">
+        <v>6.0883099999999999</v>
+      </c>
+      <c r="Z20">
+        <v>0.98934999999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>301</v>
+      </c>
+      <c r="B21" s="140">
+        <v>1500000</v>
+      </c>
+      <c r="C21">
+        <v>900000020</v>
+      </c>
+      <c r="D21" t="s">
+        <v>800</v>
+      </c>
+      <c r="E21">
+        <v>191342</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>43830.400000000001</v>
+      </c>
+      <c r="K21" s="96">
+        <v>1783330</v>
+      </c>
+      <c r="L21" s="96">
+        <v>1783330</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>19350</v>
+      </c>
+      <c r="O21">
+        <v>19350</v>
+      </c>
+      <c r="P21">
+        <v>7600</v>
+      </c>
+      <c r="Q21">
+        <v>24000</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0.89166699999999999</v>
+      </c>
+      <c r="T21">
+        <v>0.107295</v>
+      </c>
+      <c r="U21" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V21">
+        <v>138540</v>
+      </c>
+      <c r="W21">
+        <v>741060</v>
+      </c>
+      <c r="X21" s="96">
+        <v>1033330</v>
+      </c>
+      <c r="Y21">
+        <v>7.1423699999999997</v>
+      </c>
+      <c r="Z21">
+        <v>1.1606399999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>302</v>
+      </c>
+      <c r="B22" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C22">
+        <v>900000021</v>
+      </c>
+      <c r="D22" t="s">
+        <v>801</v>
+      </c>
+      <c r="E22">
+        <v>208092</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>47613.599999999999</v>
+      </c>
+      <c r="K22" s="96">
+        <v>2033330</v>
+      </c>
+      <c r="L22" s="96">
+        <v>2033330</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>9675</v>
+      </c>
+      <c r="O22">
+        <v>9675</v>
+      </c>
+      <c r="P22">
+        <v>7600</v>
+      </c>
+      <c r="Q22">
+        <v>24000</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>1.01667</v>
+      </c>
+      <c r="T22">
+        <v>0.10234</v>
+      </c>
+      <c r="U22" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V22">
+        <v>141640</v>
+      </c>
+      <c r="W22">
+        <v>744921</v>
+      </c>
+      <c r="X22" s="96">
+        <v>1033330</v>
+      </c>
+      <c r="Y22">
+        <v>6.9593100000000003</v>
+      </c>
+      <c r="Z22">
+        <v>1.13089</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>303</v>
+      </c>
+      <c r="B23" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C23">
+        <v>900000022</v>
+      </c>
+      <c r="D23" t="s">
+        <v>802</v>
+      </c>
+      <c r="E23">
+        <v>122756</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>23676.2</v>
+      </c>
+      <c r="K23" s="96">
+        <v>1550000</v>
+      </c>
+      <c r="L23" s="96">
+        <v>1550000</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>9675</v>
+      </c>
+      <c r="O23">
+        <v>9675</v>
+      </c>
+      <c r="P23">
+        <v>7600</v>
+      </c>
+      <c r="Q23">
+        <v>24000</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="T23">
+        <v>7.9197199999999995E-2</v>
+      </c>
+      <c r="U23" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V23">
+        <v>86448.3</v>
+      </c>
+      <c r="W23">
+        <v>401459</v>
+      </c>
+      <c r="X23">
+        <v>550000</v>
+      </c>
+      <c r="Y23">
+        <v>6.0883099999999999</v>
+      </c>
+      <c r="Z23">
+        <v>0.98934999999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>304</v>
+      </c>
+      <c r="B24" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C24">
+        <v>900000023</v>
+      </c>
+      <c r="D24" t="s">
+        <v>803</v>
+      </c>
+      <c r="E24">
+        <v>122756</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>23676.2</v>
+      </c>
+      <c r="K24" s="96">
+        <v>1550000</v>
+      </c>
+      <c r="L24" s="96">
+        <v>1550000</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>9675</v>
+      </c>
+      <c r="O24">
+        <v>9675</v>
+      </c>
+      <c r="P24">
+        <v>7600</v>
+      </c>
+      <c r="Q24">
+        <v>24000</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="T24">
+        <v>7.9197199999999995E-2</v>
+      </c>
+      <c r="U24" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V24">
+        <v>86448.3</v>
+      </c>
+      <c r="W24">
+        <v>401459</v>
+      </c>
+      <c r="X24">
+        <v>550000</v>
+      </c>
+      <c r="Y24">
+        <v>6.0883099999999999</v>
+      </c>
+      <c r="Z24">
+        <v>0.98934999999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>305</v>
+      </c>
+      <c r="B25" s="140">
+        <v>1250000</v>
+      </c>
+      <c r="C25">
+        <v>900000024</v>
+      </c>
+      <c r="D25" t="s">
+        <v>804</v>
+      </c>
+      <c r="E25">
+        <v>102025</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>14889.3</v>
+      </c>
+      <c r="K25" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="L25" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>9675</v>
+      </c>
+      <c r="O25">
+        <v>9675</v>
+      </c>
+      <c r="P25">
+        <v>5700</v>
+      </c>
+      <c r="Q25">
+        <v>18000</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="T25">
+        <v>8.1619800000000006E-2</v>
+      </c>
+      <c r="U25" s="96">
+        <v>1500000</v>
+      </c>
+      <c r="V25">
+        <v>63229.599999999999</v>
+      </c>
+      <c r="W25">
+        <v>316480</v>
+      </c>
+      <c r="X25">
+        <v>500000</v>
+      </c>
+      <c r="Y25">
+        <v>7.6722000000000001</v>
+      </c>
+      <c r="Z25">
+        <v>1.2467299999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>306</v>
+      </c>
+      <c r="B26" s="140">
+        <v>625000</v>
+      </c>
+      <c r="C26">
+        <v>900000025</v>
+      </c>
+      <c r="D26" t="s">
+        <v>805</v>
+      </c>
+      <c r="E26">
+        <v>102025</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>14889.3</v>
+      </c>
+      <c r="K26" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="L26" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>33862.5</v>
+      </c>
+      <c r="O26">
+        <v>33862.5</v>
+      </c>
+      <c r="P26">
+        <v>5700</v>
+      </c>
+      <c r="Q26">
+        <v>18000</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="T26">
+        <v>8.1619800000000006E-2</v>
+      </c>
+      <c r="U26" s="96">
+        <v>1500000</v>
+      </c>
+      <c r="V26">
+        <v>63229.599999999999</v>
+      </c>
+      <c r="W26">
+        <v>316480</v>
+      </c>
+      <c r="X26">
+        <v>500000</v>
+      </c>
+      <c r="Y26">
+        <v>7.6722000000000001</v>
+      </c>
+      <c r="Z26">
+        <v>1.2467299999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>307</v>
+      </c>
+      <c r="B27" s="140">
+        <v>1250000</v>
+      </c>
+      <c r="C27">
+        <v>900000026</v>
+      </c>
+      <c r="D27" t="s">
+        <v>806</v>
+      </c>
+      <c r="E27">
+        <v>102025</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>14889.3</v>
+      </c>
+      <c r="K27" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="L27" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>9675</v>
+      </c>
+      <c r="O27">
+        <v>9675</v>
+      </c>
+      <c r="P27">
+        <v>5700</v>
+      </c>
+      <c r="Q27">
+        <v>18000</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="T27">
+        <v>8.1619800000000006E-2</v>
+      </c>
+      <c r="U27" s="96">
+        <v>1500000</v>
+      </c>
+      <c r="V27">
+        <v>63229.599999999999</v>
+      </c>
+      <c r="W27">
+        <v>316480</v>
+      </c>
+      <c r="X27">
+        <v>500000</v>
+      </c>
+      <c r="Y27">
+        <v>7.6722000000000001</v>
+      </c>
+      <c r="Z27">
+        <v>1.2467299999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>308</v>
+      </c>
+      <c r="B28" s="140">
+        <v>3500000</v>
+      </c>
+      <c r="C28">
+        <v>900000027</v>
+      </c>
+      <c r="D28" t="s">
+        <v>807</v>
+      </c>
+      <c r="E28">
+        <v>102025</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>14889.3</v>
+      </c>
+      <c r="K28" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="L28" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>19350</v>
+      </c>
+      <c r="O28">
+        <v>19350</v>
+      </c>
+      <c r="P28">
+        <v>15200</v>
+      </c>
+      <c r="Q28">
+        <v>48000</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0.3125</v>
+      </c>
+      <c r="T28">
+        <v>8.1619800000000006E-2</v>
+      </c>
+      <c r="U28" s="96">
+        <v>4000000</v>
+      </c>
+      <c r="V28">
+        <v>63229.599999999999</v>
+      </c>
+      <c r="W28">
+        <v>316480</v>
+      </c>
+      <c r="X28">
+        <v>500000</v>
+      </c>
+      <c r="Y28">
+        <v>7.6722000000000001</v>
+      </c>
+      <c r="Z28">
+        <v>1.2467299999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>309</v>
+      </c>
+      <c r="B29" s="140">
+        <v>1250000</v>
+      </c>
+      <c r="C29">
+        <v>900000028</v>
+      </c>
+      <c r="D29" t="s">
+        <v>808</v>
+      </c>
+      <c r="E29">
+        <v>102025</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>14889.3</v>
+      </c>
+      <c r="K29" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="L29" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>9675</v>
+      </c>
+      <c r="O29">
+        <v>9675</v>
+      </c>
+      <c r="P29">
+        <v>5700</v>
+      </c>
+      <c r="Q29">
+        <v>18000</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="T29">
+        <v>8.1619800000000006E-2</v>
+      </c>
+      <c r="U29" s="96">
+        <v>1500000</v>
+      </c>
+      <c r="V29">
+        <v>63229.599999999999</v>
+      </c>
+      <c r="W29">
+        <v>316480</v>
+      </c>
+      <c r="X29">
+        <v>500000</v>
+      </c>
+      <c r="Y29">
+        <v>7.6722000000000001</v>
+      </c>
+      <c r="Z29">
+        <v>1.2467299999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>310</v>
+      </c>
+      <c r="B30" s="140">
+        <v>1250000</v>
+      </c>
+      <c r="C30">
+        <v>900000029</v>
+      </c>
+      <c r="D30" t="s">
+        <v>809</v>
+      </c>
+      <c r="E30">
+        <v>102025</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>14889.3</v>
+      </c>
+      <c r="K30" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="L30" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>9675</v>
+      </c>
+      <c r="O30">
+        <v>9675</v>
+      </c>
+      <c r="P30">
+        <v>5700</v>
+      </c>
+      <c r="Q30">
+        <v>18000</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0.83333299999999999</v>
+      </c>
+      <c r="T30">
+        <v>8.1619800000000006E-2</v>
+      </c>
+      <c r="U30" s="96">
+        <v>1500000</v>
+      </c>
+      <c r="V30">
+        <v>63229.599999999999</v>
+      </c>
+      <c r="W30">
+        <v>316480</v>
+      </c>
+      <c r="X30">
+        <v>500000</v>
+      </c>
+      <c r="Y30">
+        <v>7.6722000000000001</v>
+      </c>
+      <c r="Z30">
+        <v>1.2467299999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>311</v>
+      </c>
+      <c r="B31" s="140">
+        <v>1250000</v>
+      </c>
+      <c r="C31">
+        <v>900000030</v>
+      </c>
+      <c r="D31" t="s">
+        <v>810</v>
+      </c>
+      <c r="E31">
+        <v>102025</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>14889.3</v>
+      </c>
+      <c r="K31" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="L31" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>4750</v>
+      </c>
+      <c r="Q31">
+        <v>15000</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0.99999899999999997</v>
+      </c>
+      <c r="T31">
+        <v>8.1619800000000006E-2</v>
+      </c>
+      <c r="U31" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="V31">
+        <v>63229.599999999999</v>
+      </c>
+      <c r="W31">
+        <v>316480</v>
+      </c>
+      <c r="X31">
+        <v>500000</v>
+      </c>
+      <c r="Y31">
+        <v>7.6722000000000001</v>
+      </c>
+      <c r="Z31">
+        <v>1.2467299999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>312</v>
+      </c>
+      <c r="B32" s="140">
+        <v>1250000</v>
+      </c>
+      <c r="C32">
+        <v>900000031</v>
+      </c>
+      <c r="D32" t="s">
+        <v>811</v>
+      </c>
+      <c r="E32">
+        <v>102025</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>14889.3</v>
+      </c>
+      <c r="K32" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="L32" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>4750</v>
+      </c>
+      <c r="Q32">
+        <v>15000</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0.99999899999999997</v>
+      </c>
+      <c r="T32">
+        <v>8.1619800000000006E-2</v>
+      </c>
+      <c r="U32" s="96">
+        <v>1250000</v>
+      </c>
+      <c r="V32">
+        <v>63229.599999999999</v>
+      </c>
+      <c r="W32">
+        <v>316480</v>
+      </c>
+      <c r="X32">
+        <v>500000</v>
+      </c>
+      <c r="Y32">
+        <v>7.6722000000000001</v>
+      </c>
+      <c r="Z32">
+        <v>1.2467299999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>313</v>
+      </c>
+      <c r="B33" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C33">
+        <v>900000032</v>
+      </c>
+      <c r="D33" t="s">
+        <v>812</v>
+      </c>
+      <c r="E33">
+        <v>208307</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>18406.599999999999</v>
+      </c>
+      <c r="K33" s="96">
+        <v>1564620</v>
+      </c>
+      <c r="L33" s="96">
+        <v>1564620</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>6650</v>
+      </c>
+      <c r="Q33">
+        <v>21000</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0.89406699999999995</v>
+      </c>
+      <c r="T33">
+        <v>0.133136</v>
+      </c>
+      <c r="U33" s="96">
+        <v>1750000</v>
+      </c>
+      <c r="V33">
+        <v>86586.8</v>
+      </c>
+      <c r="W33">
+        <v>577489</v>
+      </c>
+      <c r="X33">
+        <v>675000</v>
+      </c>
+      <c r="Y33">
+        <v>7.5830700000000002</v>
+      </c>
+      <c r="Z33">
+        <v>1.2322500000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>314</v>
+      </c>
+      <c r="B34" s="140">
+        <v>2000000</v>
+      </c>
+      <c r="C34">
+        <v>900000033</v>
+      </c>
+      <c r="D34" t="s">
+        <v>813</v>
+      </c>
+      <c r="E34">
+        <v>392526</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>35334.5</v>
+      </c>
+      <c r="K34" s="96">
+        <v>3116670</v>
+      </c>
+      <c r="L34" s="96">
+        <v>3116670</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>7600</v>
+      </c>
+      <c r="Q34">
+        <v>24000</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>1.55833</v>
+      </c>
+      <c r="T34">
+        <v>0.125944</v>
+      </c>
+      <c r="U34" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V34">
+        <v>139875</v>
+      </c>
+      <c r="W34">
+        <v>756686</v>
+      </c>
+      <c r="X34">
+        <v>949684</v>
+      </c>
+      <c r="Y34">
+        <v>6.5369200000000003</v>
+      </c>
+      <c r="Z34">
+        <v>1.0622499999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>315</v>
+      </c>
+      <c r="B35" s="140">
+        <v>2000000</v>
+      </c>
+      <c r="C35">
+        <v>900000034</v>
+      </c>
+      <c r="D35" t="s">
+        <v>814</v>
+      </c>
+      <c r="E35">
+        <v>392526</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>35334.5</v>
+      </c>
+      <c r="K35" s="96">
+        <v>3116670</v>
+      </c>
+      <c r="L35" s="96">
+        <v>3116670</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>7600</v>
+      </c>
+      <c r="Q35">
+        <v>24000</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>1.55833</v>
+      </c>
+      <c r="T35">
+        <v>0.125944</v>
+      </c>
+      <c r="U35" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V35">
+        <v>139875</v>
+      </c>
+      <c r="W35">
+        <v>756686</v>
+      </c>
+      <c r="X35">
+        <v>949684</v>
+      </c>
+      <c r="Y35">
+        <v>6.5369200000000003</v>
+      </c>
+      <c r="Z35">
+        <v>1.0622499999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>316</v>
+      </c>
+      <c r="B36" s="140">
+        <v>1750000</v>
+      </c>
+      <c r="C36">
+        <v>900000035</v>
+      </c>
+      <c r="D36" t="s">
+        <v>815</v>
+      </c>
+      <c r="E36">
+        <v>208307</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>18406.599999999999</v>
+      </c>
+      <c r="K36" s="96">
+        <v>1564620</v>
+      </c>
+      <c r="L36" s="96">
+        <v>1564620</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>9675</v>
+      </c>
+      <c r="O36">
+        <v>9675</v>
+      </c>
+      <c r="P36">
+        <v>7600</v>
+      </c>
+      <c r="Q36">
+        <v>24000</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0.78230900000000003</v>
+      </c>
+      <c r="T36">
+        <v>0.133136</v>
+      </c>
+      <c r="U36" s="96">
+        <v>2000000</v>
+      </c>
+      <c r="V36">
+        <v>86586.8</v>
+      </c>
+      <c r="W36">
+        <v>577489</v>
+      </c>
+      <c r="X36">
+        <v>675000</v>
+      </c>
+      <c r="Y36">
+        <v>7.5830700000000002</v>
+      </c>
+      <c r="Z36">
+        <v>1.2322500000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C97D5646-F693-41CD-9F31-2D929AB6EE21}">
+  <sheetPr codeName="Sheet11"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:X254"/>
@@ -30503,72 +35022,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="129" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
-      <c r="U1" s="101"/>
-      <c r="V1" s="101"/>
-      <c r="W1" s="101"/>
-      <c r="X1" s="101"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
+      <c r="X1" s="129"/>
     </row>
     <row r="2" spans="1:24" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="95" t="s">
+      <c r="B2" s="130"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98" t="s">
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="126" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="103" t="s">
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="131" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="104" t="s">
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="132" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="97"/>
-      <c r="R2" s="96" t="s">
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="124" t="s">
         <v>88</v>
       </c>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="100" t="s">
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="128" t="s">
         <v>89</v>
       </c>
-      <c r="V2" s="97"/>
-      <c r="W2" s="97"/>
-      <c r="X2" s="97"/>
+      <c r="V2" s="125"/>
+      <c r="W2" s="125"/>
+      <c r="X2" s="125"/>
     </row>
     <row r="3" spans="1:24" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -39601,7 +44120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:Z144"/>
@@ -39629,64 +44148,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="129" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="125"/>
+      <c r="P1" s="125"/>
+      <c r="Q1" s="125"/>
+      <c r="R1" s="125"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
+      <c r="U1" s="125"/>
     </row>
     <row r="2" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="134" t="s">
+      <c r="A2" s="136" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="133" t="s">
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="135" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="132" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="134" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="103" t="s">
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="131" t="s">
         <v>157</v>
       </c>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
-      <c r="P2" s="96" t="s">
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="124" t="s">
         <v>158</v>
       </c>
-      <c r="Q2" s="100" t="s">
+      <c r="Q2" s="128" t="s">
         <v>89</v>
       </c>
-      <c r="R2" s="97"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
     </row>
     <row r="3" spans="1:26" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -39884,29 +44403,29 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="131" t="s">
+      <c r="A6" s="133" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="97"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="97"/>
-      <c r="O6" s="97"/>
-      <c r="P6" s="97"/>
-      <c r="Q6" s="97"/>
-      <c r="R6" s="97"/>
-      <c r="S6" s="97"/>
-      <c r="T6" s="97"/>
-      <c r="U6" s="97"/>
+      <c r="B6" s="125"/>
+      <c r="C6" s="125"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="125"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="125"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="125"/>
+      <c r="M6" s="125"/>
+      <c r="N6" s="125"/>
+      <c r="O6" s="125"/>
+      <c r="P6" s="125"/>
+      <c r="Q6" s="125"/>
+      <c r="R6" s="125"/>
+      <c r="S6" s="125"/>
+      <c r="T6" s="125"/>
+      <c r="U6" s="125"/>
     </row>
     <row r="7" spans="1:26" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
@@ -43545,8 +48064,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A27E21-29C7-4654-B257-6150E506C856}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:O139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -50103,1407 +54623,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="20"/>
-    </row>
-    <row r="3" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="20" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="20" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="20" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="20" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="20" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="20"/>
-    </row>
-    <row r="10" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="20" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="20"/>
-    </row>
-    <row r="13" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="20" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="20"/>
-    </row>
-    <row r="16" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="20" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="20" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="20" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="20" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="20"/>
-    </row>
-    <row r="22" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="20" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="20"/>
-    </row>
-    <row r="25" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="20" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="20"/>
-    </row>
-    <row r="28" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>245</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:BF40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="9" width="19" customWidth="1"/>
-    <col min="10" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="17" width="15" customWidth="1"/>
-    <col min="18" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="15" customWidth="1"/>
-    <col min="26" max="26" width="18" customWidth="1"/>
-    <col min="27" max="27" width="19" customWidth="1"/>
-    <col min="28" max="28" width="21" customWidth="1"/>
-    <col min="29" max="29" width="16" customWidth="1"/>
-    <col min="30" max="30" width="25" customWidth="1"/>
-    <col min="31" max="32" width="18" customWidth="1"/>
-    <col min="33" max="52" width="15" customWidth="1"/>
-    <col min="53" max="53" width="18" customWidth="1"/>
-    <col min="54" max="54" width="21" customWidth="1"/>
-    <col min="55" max="55" width="15" customWidth="1"/>
-    <col min="56" max="56" width="18" customWidth="1"/>
-    <col min="57" max="58" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:58" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="135" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
-      <c r="AD1" s="97"/>
-      <c r="AE1" s="97"/>
-      <c r="AF1" s="97"/>
-      <c r="AG1" s="97"/>
-      <c r="AH1" s="97"/>
-      <c r="AI1" s="97"/>
-      <c r="AJ1" s="97"/>
-      <c r="AK1" s="97"/>
-      <c r="AL1" s="97"/>
-      <c r="AM1" s="97"/>
-      <c r="AN1" s="97"/>
-      <c r="AO1" s="97"/>
-      <c r="AP1" s="97"/>
-      <c r="AQ1" s="97"/>
-      <c r="AR1" s="97"/>
-      <c r="AS1" s="97"/>
-      <c r="AT1" s="97"/>
-      <c r="AU1" s="97"/>
-      <c r="AV1" s="97"/>
-      <c r="AW1" s="97"/>
-      <c r="AX1" s="97"/>
-      <c r="AY1" s="97"/>
-      <c r="AZ1" s="97"/>
-    </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="U2" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="V2" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="X2" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y2" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z2" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA2" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC2" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD2" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE2" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF2" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="BA2" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="BB2" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="BC2" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="BD2" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="BE2" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="BF2" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="26"/>
-      <c r="AC3" s="26"/>
-      <c r="AD3" s="26"/>
-      <c r="AE3" s="26"/>
-      <c r="AF3" s="26"/>
-    </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="29"/>
-    </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-    </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="29"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-    </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-      <c r="W7" s="29"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-    </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="29"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="29"/>
-      <c r="AC8" s="29"/>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="29"/>
-    </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-    </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="Q10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="AC10" s="29"/>
-      <c r="BC10" s="29"/>
-      <c r="BD10" s="29"/>
-      <c r="BE10" s="29"/>
-      <c r="BF10" s="29"/>
-    </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29"/>
-      <c r="AC11" s="29"/>
-      <c r="AD11" s="29"/>
-      <c r="AE11" s="29"/>
-      <c r="AF11" s="29"/>
-      <c r="BA11" s="29"/>
-      <c r="BB11" s="29"/>
-    </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="29"/>
-      <c r="N12" s="28"/>
-      <c r="Q12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AC12" s="29"/>
-    </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29"/>
-      <c r="Y13" s="29"/>
-      <c r="Z13" s="29"/>
-      <c r="AA13" s="29"/>
-      <c r="AC13" s="29"/>
-      <c r="AD13" s="29"/>
-      <c r="AE13" s="29"/>
-      <c r="AF13" s="29"/>
-      <c r="BA13" s="29"/>
-      <c r="BB13" s="29"/>
-    </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="29"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="29"/>
-      <c r="AD14" s="29"/>
-      <c r="AE14" s="29"/>
-      <c r="AF14" s="29"/>
-    </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29"/>
-      <c r="Y15" s="29"/>
-      <c r="Z15" s="29"/>
-      <c r="AA15" s="29"/>
-      <c r="AC15" s="29"/>
-      <c r="AD15" s="29"/>
-      <c r="AE15" s="29"/>
-      <c r="AF15" s="29"/>
-      <c r="BA15" s="29"/>
-      <c r="BB15" s="29"/>
-    </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="29"/>
-      <c r="N16" s="28"/>
-      <c r="Q16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="Z16" s="29"/>
-      <c r="AC16" s="29"/>
-    </row>
-    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="28"/>
-      <c r="O17" s="29"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="V17" s="29"/>
-      <c r="W17" s="29"/>
-      <c r="X17" s="29"/>
-      <c r="Y17" s="29"/>
-      <c r="Z17" s="29"/>
-      <c r="AA17" s="29"/>
-      <c r="AC17" s="29"/>
-      <c r="AD17" s="29"/>
-      <c r="AE17" s="29"/>
-      <c r="AF17" s="29"/>
-      <c r="BA17" s="29"/>
-      <c r="BB17" s="29"/>
-    </row>
-    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="29"/>
-      <c r="N18" s="28"/>
-      <c r="Q18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="Z18" s="29"/>
-      <c r="AC18" s="29"/>
-    </row>
-    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="29"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="29"/>
-      <c r="Y19" s="29"/>
-      <c r="Z19" s="29"/>
-      <c r="AA19" s="29"/>
-      <c r="AC19" s="29"/>
-      <c r="AD19" s="29"/>
-      <c r="AE19" s="29"/>
-      <c r="AF19" s="29"/>
-      <c r="BA19" s="29"/>
-      <c r="BB19" s="29"/>
-    </row>
-    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="29"/>
-      <c r="N20" s="28"/>
-      <c r="Q20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="Z20" s="29"/>
-      <c r="AC20" s="29"/>
-    </row>
-    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
-      <c r="V21" s="29"/>
-      <c r="W21" s="29"/>
-      <c r="X21" s="29"/>
-      <c r="Y21" s="29"/>
-      <c r="Z21" s="29"/>
-      <c r="AA21" s="29"/>
-      <c r="AC21" s="29"/>
-      <c r="AD21" s="29"/>
-      <c r="AE21" s="29"/>
-      <c r="AF21" s="29"/>
-      <c r="BA21" s="29"/>
-      <c r="BB21" s="29"/>
-    </row>
-    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="29"/>
-      <c r="N22" s="28"/>
-      <c r="Q22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="Z22" s="29"/>
-      <c r="AC22" s="29"/>
-    </row>
-    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
-      <c r="AE23" s="29"/>
-      <c r="AF23" s="29"/>
-      <c r="BA23" s="29"/>
-      <c r="BB23" s="29"/>
-    </row>
-    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="29"/>
-      <c r="N24" s="28"/>
-      <c r="Q24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="Z24" s="29"/>
-      <c r="AC24" s="29"/>
-    </row>
-    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="V25" s="29"/>
-      <c r="W25" s="29"/>
-      <c r="X25" s="29"/>
-      <c r="Y25" s="29"/>
-      <c r="Z25" s="29"/>
-      <c r="AA25" s="29"/>
-      <c r="AC25" s="29"/>
-      <c r="AD25" s="29"/>
-      <c r="AE25" s="29"/>
-      <c r="AF25" s="29"/>
-      <c r="BA25" s="29"/>
-      <c r="BB25" s="29"/>
-    </row>
-    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="29"/>
-      <c r="N26" s="28"/>
-      <c r="Q26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AC26" s="29"/>
-    </row>
-    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="29"/>
-      <c r="Y27" s="29"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="29"/>
-      <c r="AE27" s="29"/>
-      <c r="AF27" s="29"/>
-      <c r="BA27" s="29"/>
-      <c r="BB27" s="29"/>
-    </row>
-    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="29"/>
-      <c r="X28" s="29"/>
-      <c r="Y28" s="29"/>
-      <c r="Z28" s="29"/>
-      <c r="AA28" s="29"/>
-      <c r="AB28" s="29"/>
-      <c r="AC28" s="29"/>
-      <c r="AD28" s="29"/>
-      <c r="AE28" s="29"/>
-      <c r="AF28" s="29"/>
-    </row>
-    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A29" s="28"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="29"/>
-      <c r="AF29" s="29"/>
-      <c r="BA29" s="29"/>
-      <c r="BB29" s="29"/>
-    </row>
-    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
-      <c r="W30" s="29"/>
-      <c r="X30" s="29"/>
-      <c r="Y30" s="29"/>
-      <c r="Z30" s="29"/>
-      <c r="AA30" s="29"/>
-      <c r="AB30" s="29"/>
-      <c r="AC30" s="29"/>
-      <c r="AD30" s="29"/>
-      <c r="AE30" s="29"/>
-      <c r="AF30" s="29"/>
-    </row>
-    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="Q31" s="29"/>
-      <c r="T31" s="29"/>
-      <c r="AC31" s="29"/>
-      <c r="BC31" s="29"/>
-      <c r="BE31" s="29"/>
-    </row>
-    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="Q32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="BC32" s="29"/>
-      <c r="BD32" s="29"/>
-      <c r="BE32" s="29"/>
-      <c r="BF32" s="29"/>
-    </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A33" s="28"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="Q33" s="29"/>
-      <c r="T33" s="29"/>
-      <c r="AC33" s="29"/>
-      <c r="BC33" s="29"/>
-      <c r="BE33" s="29"/>
-    </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A34" s="28"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="Q34" s="29"/>
-      <c r="T34" s="29"/>
-      <c r="AC34" s="29"/>
-      <c r="BC34" s="29"/>
-      <c r="BE34" s="29"/>
-    </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A35" s="28"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="Q35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="AC35" s="29"/>
-      <c r="BC35" s="29"/>
-      <c r="BE35" s="29"/>
-    </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A36" s="28"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="Q36" s="29"/>
-      <c r="T36" s="29"/>
-      <c r="AC36" s="29"/>
-      <c r="BC36" s="29"/>
-      <c r="BE36" s="29"/>
-    </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A37" s="28"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="Q37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="AC37" s="29"/>
-      <c r="BC37" s="29"/>
-      <c r="BE37" s="29"/>
-    </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="Q38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="AC38" s="29"/>
-      <c r="BC38" s="29"/>
-      <c r="BE38" s="29"/>
-    </row>
-    <row r="39" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="Q39" s="29"/>
-      <c r="T39" s="29"/>
-      <c r="AC39" s="29"/>
-      <c r="BC39" s="29"/>
-      <c r="BE39" s="29"/>
-    </row>
-    <row r="40" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A40" s="28"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="Q40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="BC40" s="29"/>
-      <c r="BE40" s="29"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AZ1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>